--- a/base_datas/media_porte_detalhamento.xlsx
+++ b/base_datas/media_porte_detalhamento.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>populacao_24</t>
+          <t>populacao_25</t>
         </is>
       </c>
     </row>
@@ -603,133 +603,133 @@
         </is>
       </c>
       <c r="B2">
-        <v>549.4168163591125</v>
+        <v>641.355133017211</v>
       </c>
       <c r="C2">
-        <v>156.3808654497147</v>
+        <v>149.1674542973497</v>
       </c>
       <c r="D2">
-        <v>5819.975403108084</v>
+        <v>6449.55562452665</v>
       </c>
       <c r="E2">
-        <v>299.7682831078441</v>
+        <v>345.9756905494411</v>
       </c>
       <c r="F2">
-        <v>500.9684538778369</v>
+        <v>588.8030153479945</v>
       </c>
       <c r="G2">
-        <v>45.69707978517246</v>
+        <v>50.14536401644651</v>
       </c>
       <c r="H2">
-        <v>19.36177749173573</v>
+        <v>17.80077598319937</v>
       </c>
       <c r="I2">
-        <v>213.9986885548085</v>
+        <v>225.1239468787671</v>
       </c>
       <c r="J2">
-        <v>63.35114646392111</v>
+        <v>64.74575855188407</v>
       </c>
       <c r="K2">
-        <v>41.79611196211873</v>
+        <v>2.545594226084234</v>
       </c>
       <c r="L2">
-        <v>3434.642889720832</v>
+        <v>3858.347648087471</v>
       </c>
       <c r="M2">
-        <v>1375.54954108741</v>
+        <v>1495.89553198412</v>
       </c>
       <c r="N2">
-        <v>1010.541067624392</v>
+        <v>1095.31244445506</v>
       </c>
       <c r="O2">
-        <v>191.8394710254275</v>
+        <v>231.615350504633</v>
       </c>
       <c r="P2">
-        <v>87.56514912812386</v>
+        <v>108.6760030592472</v>
       </c>
       <c r="Q2">
-        <v>2.008150827839334</v>
+        <v>2.946798168783711</v>
       </c>
       <c r="R2">
-        <v>20.17443846114332</v>
+        <v>26.57264291966604</v>
       </c>
       <c r="S2">
-        <v>61.82858246127102</v>
+        <v>60.31796272498978</v>
       </c>
       <c r="T2">
-        <v>69.62599818534926</v>
+        <v>101.2797072423534</v>
       </c>
       <c r="U2">
-        <v>59.31618941320696</v>
+        <v>66.88002430588655</v>
       </c>
       <c r="V2">
-        <v>211.7413586901639</v>
+        <v>229.5514765346402</v>
       </c>
       <c r="W2">
-        <v>161.5135713575636</v>
+        <v>190.3275007169333</v>
       </c>
       <c r="Z2">
-        <v>6.37950982920562</v>
+        <v>7.58650199727195</v>
       </c>
       <c r="AA2">
-        <v>22.54571592252723</v>
+        <v>23.73182637910688</v>
       </c>
       <c r="AB2">
-        <v>29.88003592395086</v>
+        <v>32.93660227450981</v>
       </c>
       <c r="AC2">
-        <v>1.462972737227358E-16</v>
+        <v>2.031782133562702E-16</v>
       </c>
       <c r="AD2">
-        <v>7.79545105573825</v>
+        <v>9.038566487127381</v>
       </c>
       <c r="AE2">
-        <v>9.715690975353615</v>
+        <v>11.30369209689145</v>
       </c>
       <c r="AF2">
-        <v>37.57785826801359</v>
+        <v>35.40463198512754</v>
       </c>
       <c r="AG2">
-        <v>9.655502130850087</v>
+        <v>6.061112304616553</v>
       </c>
       <c r="AH2">
-        <v>2025.10396307044</v>
+        <v>2247.141470001221</v>
       </c>
       <c r="AJ2">
-        <v>166.6917629813262</v>
+        <v>173.8707650975027</v>
       </c>
       <c r="AK2">
-        <v>585.4099754447005</v>
+        <v>663.5359858511503</v>
       </c>
       <c r="AL2">
-        <v>125.2154306289127</v>
+        <v>128.9035362995671</v>
       </c>
       <c r="AM2">
-        <v>507.0945920514752</v>
+        <v>526.2298927327635</v>
       </c>
       <c r="AN2">
-        <v>32.26031691751002</v>
+        <v>30.52908636273312</v>
       </c>
       <c r="AO2">
-        <v>135.7149862436033</v>
+        <v>126.4163013688064</v>
       </c>
       <c r="AP2">
-        <v>1054.011340318775</v>
+        <v>1132.323221225155</v>
       </c>
       <c r="AQ2">
-        <v>117.4697747492557</v>
+        <v>127.5119427805369</v>
       </c>
       <c r="AR2">
-        <v>87.20998417490506</v>
+        <v>104.9790533344364</v>
       </c>
       <c r="AS2">
-        <v>11.28991989908589</v>
+        <v>15.94498026155901</v>
       </c>
       <c r="AT2">
-        <v>33.37480272920787</v>
+        <v>60.55100943272583</v>
       </c>
       <c r="AU2">
-        <v>123.0610086994272</v>
+        <v>126.3082256550515</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -742,133 +742,133 @@
         </is>
       </c>
       <c r="B3">
-        <v>1220.225719465266</v>
+        <v>1358.178217291227</v>
       </c>
       <c r="C3">
-        <v>228.4244452627582</v>
+        <v>239.474649922203</v>
       </c>
       <c r="D3">
-        <v>3952.053817004274</v>
+        <v>4347.084449692204</v>
       </c>
       <c r="E3">
-        <v>513.4609368192213</v>
+        <v>586.0103549438049</v>
       </c>
       <c r="F3">
-        <v>1123.019898626901</v>
+        <v>1253.775846563763</v>
       </c>
       <c r="G3">
-        <v>94.60352712909845</v>
+        <v>103.4165531249799</v>
       </c>
       <c r="H3">
-        <v>7.896615393636334</v>
+        <v>4.693566968848419</v>
       </c>
       <c r="I3">
-        <v>173.351524917799</v>
+        <v>183.6525681116702</v>
       </c>
       <c r="J3">
-        <v>91.00252207136381</v>
+        <v>93.74860548761032</v>
       </c>
       <c r="K3">
-        <v>0.3015163275138856</v>
+        <v>0.3092371532374829</v>
       </c>
       <c r="L3">
-        <v>1808.247389592512</v>
+        <v>2030.887425656508</v>
       </c>
       <c r="M3">
-        <v>1375.05126511702</v>
+        <v>1495.734154255548</v>
       </c>
       <c r="N3">
-        <v>768.7551622947412</v>
+        <v>828.9613592929634</v>
       </c>
       <c r="O3">
-        <v>249.5249812980668</v>
+        <v>311.9937216424929</v>
       </c>
       <c r="P3">
-        <v>184.0845690859562</v>
+        <v>190.947379645138</v>
       </c>
       <c r="Q3">
-        <v>0.2973005377239345</v>
+        <v>0.387531794467433</v>
       </c>
       <c r="R3">
-        <v>4.261633186351126</v>
+        <v>1.907603964804308</v>
       </c>
       <c r="S3">
-        <v>123.72547412319</v>
+        <v>129.6906854154552</v>
       </c>
       <c r="T3">
-        <v>294.7559551521182</v>
+        <v>325.2061812920231</v>
       </c>
       <c r="U3">
-        <v>100.988088109687</v>
+        <v>115.6105262530484</v>
       </c>
       <c r="V3">
-        <v>488.5768077920155</v>
+        <v>541.0212069963408</v>
       </c>
       <c r="W3">
-        <v>237.9304365947446</v>
+        <v>267.8084267820951</v>
       </c>
       <c r="Z3">
-        <v>4.48814633078491</v>
+        <v>15.87341686138365</v>
       </c>
       <c r="AA3">
-        <v>40.63111136733944</v>
+        <v>42.29789612192275</v>
       </c>
       <c r="AB3">
-        <v>58.91261963133503</v>
+        <v>65.73390712060267</v>
       </c>
       <c r="AC3">
-        <v>1.72950460120984E-15</v>
+        <v>-1.781256888914672E-15</v>
       </c>
       <c r="AD3">
-        <v>1.481326625685871</v>
+        <v>1.178378772147617</v>
       </c>
       <c r="AE3">
-        <v>18.77893766801164</v>
+        <v>2.386465140010241</v>
       </c>
       <c r="AF3">
-        <v>29.38152068091843</v>
+        <v>30.28694649276918</v>
       </c>
       <c r="AG3">
-        <v>5.510151629173122</v>
+        <v>0.5293785905511025</v>
       </c>
       <c r="AH3">
-        <v>843.7454820355397</v>
+        <v>967.1231410675676</v>
       </c>
       <c r="AJ3">
-        <v>136.1609712814351</v>
+        <v>158.6187451414569</v>
       </c>
       <c r="AK3">
-        <v>527.3679624108645</v>
+        <v>573.2524544216083</v>
       </c>
       <c r="AL3">
-        <v>86.26875582743497</v>
+        <v>86.23443480497994</v>
       </c>
       <c r="AM3">
-        <v>207.0908935128407</v>
+        <v>199.985025930053</v>
       </c>
       <c r="AN3">
-        <v>14.22277473001678</v>
+        <v>14.46430749070402</v>
       </c>
       <c r="AO3">
-        <v>48.69427676325645</v>
+        <v>53.07770475459184</v>
       </c>
       <c r="AP3">
-        <v>998.8439332705275</v>
+        <v>1074.243897251647</v>
       </c>
       <c r="AQ3">
-        <v>206.4992537472147</v>
+        <v>223.780528155867</v>
       </c>
       <c r="AR3">
-        <v>102.7999826274989</v>
+        <v>120.8512758187893</v>
       </c>
       <c r="AS3">
-        <v>5.521136634119836</v>
+        <v>7.833029357521081</v>
       </c>
       <c r="AT3">
-        <v>23.97642940911434</v>
+        <v>24.04645570079388</v>
       </c>
       <c r="AU3">
-        <v>64.4815998677302</v>
+        <v>72.5821621423833</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -881,133 +881,133 @@
         </is>
       </c>
       <c r="B4">
-        <v>683.7584210499662</v>
+        <v>782.0710370890309</v>
       </c>
       <c r="C4">
-        <v>165.7814756011512</v>
+        <v>179.8921049289116</v>
       </c>
       <c r="D4">
-        <v>5065.801296550819</v>
+        <v>5575.483239845395</v>
       </c>
       <c r="E4">
-        <v>320.2900648269564</v>
+        <v>387.1335409423273</v>
       </c>
       <c r="F4">
-        <v>620.7603198999205</v>
+        <v>708.3765379184455</v>
       </c>
       <c r="G4">
-        <v>60.82683470883153</v>
+        <v>69.53641511149135</v>
       </c>
       <c r="H4">
-        <v>13.12172856653987</v>
+        <v>23.68349764612323</v>
       </c>
       <c r="I4">
-        <v>198.0056360777324</v>
+        <v>216.9437462363239</v>
       </c>
       <c r="J4">
-        <v>71.12428371284993</v>
+        <v>75.6109343033897</v>
       </c>
       <c r="K4">
-        <v>1.435064217402416</v>
+        <v>3.578608439804047</v>
       </c>
       <c r="L4">
-        <v>2855.738711263837</v>
+        <v>3189.56866293319</v>
       </c>
       <c r="M4">
-        <v>1256.971256477495</v>
+        <v>1357.873213362478</v>
       </c>
       <c r="N4">
-        <v>953.0913288094873</v>
+        <v>1029.029864860833</v>
       </c>
       <c r="O4">
-        <v>186.0340127521739</v>
+        <v>253.7864487667663</v>
       </c>
       <c r="P4">
-        <v>102.2626672666544</v>
+        <v>113.9243562679543</v>
       </c>
       <c r="Q4">
-        <v>2.427611934003728</v>
+        <v>2.527933557288459</v>
       </c>
       <c r="R4">
-        <v>8.3146730514505</v>
+        <v>8.004472591020871</v>
       </c>
       <c r="S4">
-        <v>72.877249041577</v>
+        <v>66.7396941348407</v>
       </c>
       <c r="T4">
-        <v>126.6123586163441</v>
+        <v>146.9354950362951</v>
       </c>
       <c r="U4">
-        <v>64.3359090609473</v>
+        <v>79.44784458312563</v>
       </c>
       <c r="V4">
-        <v>254.3345124839394</v>
+        <v>282.3763718173377</v>
       </c>
       <c r="W4">
-        <v>175.8423026596535</v>
+        <v>202.5719731694756</v>
       </c>
       <c r="Z4">
-        <v>5.401038509925935</v>
+        <v>3.720695182853818</v>
       </c>
       <c r="AA4">
-        <v>30.22706301899838</v>
+        <v>35.44378061477808</v>
       </c>
       <c r="AB4">
-        <v>37.03694031171195</v>
+        <v>40.8387719287887</v>
       </c>
       <c r="AC4">
-        <v>5.658314569561789E-17</v>
+        <v>-5.34473712707361E-16</v>
       </c>
       <c r="AD4">
-        <v>3.190395392481452</v>
+        <v>17.90405419186754</v>
       </c>
       <c r="AE4">
-        <v>22.44969476882906</v>
+        <v>7.221226896047424</v>
       </c>
       <c r="AF4">
-        <v>35.31494447656709</v>
+        <v>32.38174782318656</v>
       </c>
       <c r="AG4">
-        <v>4.061797982094433</v>
+        <v>19.64641293477783</v>
       </c>
       <c r="AH4">
-        <v>1469.51707718747</v>
+        <v>1641.63241874457</v>
       </c>
       <c r="AJ4">
-        <v>190.1909038082175</v>
+        <v>202.4100731640795</v>
       </c>
       <c r="AK4">
-        <v>559.214492123717</v>
+        <v>628.5257793394405</v>
       </c>
       <c r="AL4">
-        <v>119.9838514378827</v>
+        <v>121.1539164371629</v>
       </c>
       <c r="AM4">
-        <v>496.8539187699448</v>
+        <v>512.1970139883547</v>
       </c>
       <c r="AN4">
-        <v>27.31823979749747</v>
+        <v>25.39897126935889</v>
       </c>
       <c r="AO4">
-        <v>113.4366461517572</v>
+        <v>98.77809681491497</v>
       </c>
       <c r="AP4">
-        <v>941.95379219414</v>
+        <v>1006.87981271626</v>
       </c>
       <c r="AQ4">
-        <v>135.7304527780872</v>
+        <v>148.7135737902597</v>
       </c>
       <c r="AR4">
-        <v>90.43741694040284</v>
+        <v>100.1590995622079</v>
       </c>
       <c r="AS4">
-        <v>8.230883145684309</v>
+        <v>11.59585220062118</v>
       </c>
       <c r="AT4">
-        <v>36.28730856384785</v>
+        <v>39.58463350105061</v>
       </c>
       <c r="AU4">
-        <v>94.7579890947204</v>
+        <v>101.4769074885261</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1020,133 +1020,133 @@
         </is>
       </c>
       <c r="B5">
-        <v>1503.955991776769</v>
+        <v>1654.605333174278</v>
       </c>
       <c r="C5">
-        <v>242.5782231417568</v>
+        <v>266.1618779170148</v>
       </c>
       <c r="D5">
-        <v>3674.637856709958</v>
+        <v>3880.117245428773</v>
       </c>
       <c r="E5">
-        <v>596.3628276717868</v>
+        <v>642.5697113154779</v>
       </c>
       <c r="F5">
-        <v>1386.214890768267</v>
+        <v>1524.371166048377</v>
       </c>
       <c r="G5">
-        <v>115.6620446514408</v>
+        <v>128.5746083758499</v>
       </c>
       <c r="H5">
-        <v>5.082137761704114</v>
+        <v>4.168194069896309</v>
       </c>
       <c r="I5">
-        <v>178.9147136104655</v>
+        <v>202.3400772647415</v>
       </c>
       <c r="J5">
-        <v>94.18902049488797</v>
+        <v>98.22798407305467</v>
       </c>
       <c r="K5">
-        <v>0.8265832777278195</v>
+        <v>0.8124056996125266</v>
       </c>
       <c r="L5">
-        <v>1609.138853888726</v>
+        <v>1666.66376223887</v>
       </c>
       <c r="M5">
-        <v>1344.895590329544</v>
+        <v>1436.349957008282</v>
       </c>
       <c r="N5">
-        <v>720.6034124916875</v>
+        <v>777.103526181621</v>
       </c>
       <c r="O5">
-        <v>293.1809891353317</v>
+        <v>339.1861300569439</v>
       </c>
       <c r="P5">
-        <v>172.5321634317044</v>
+        <v>172.2782750836084</v>
       </c>
       <c r="Q5">
-        <v>1.501683758939342</v>
+        <v>0.199959403109301</v>
       </c>
       <c r="R5">
-        <v>0.004352207223269753</v>
+        <v>0.265708805789203</v>
       </c>
       <c r="S5">
-        <v>144.6976055381707</v>
+        <v>147.0471321417577</v>
       </c>
       <c r="T5">
-        <v>363.2928285077124</v>
+        <v>400.3336854639896</v>
       </c>
       <c r="U5">
-        <v>114.8734431809503</v>
+        <v>121.3243626860779</v>
       </c>
       <c r="V5">
-        <v>644.0484519768249</v>
+        <v>712.858262143802</v>
       </c>
       <c r="W5">
-        <v>263.4855268821343</v>
+        <v>289.054032436056</v>
       </c>
       <c r="Z5">
-        <v>1.863955080999107</v>
+        <v>0.9828286180995748</v>
       </c>
       <c r="AA5">
-        <v>47.61421383512789</v>
+        <v>52.2236361703611</v>
       </c>
       <c r="AB5">
-        <v>71.51405488174223</v>
+        <v>80.56435567342869</v>
       </c>
       <c r="AC5">
-        <v>2.932020729919325E-15</v>
+        <v>-3.260788142078629E-15</v>
       </c>
       <c r="AD5">
-        <v>1.087972278701519</v>
+        <v>1.008184964889104</v>
       </c>
       <c r="AE5">
-        <v>1.086238029261301</v>
+        <v>0.1123689410923503</v>
       </c>
       <c r="AF5">
-        <v>30.24486041102003</v>
+        <v>24.46553885884667</v>
       </c>
       <c r="AG5">
-        <v>0.666726888826831</v>
+        <v>0.4170401890482442</v>
       </c>
       <c r="AH5">
-        <v>590.9863048120827</v>
+        <v>642.3329431366636</v>
       </c>
       <c r="AJ5">
-        <v>306.4128901987074</v>
+        <v>295.2510118672113</v>
       </c>
       <c r="AK5">
-        <v>482.3429854262674</v>
+        <v>488.7233630457664</v>
       </c>
       <c r="AL5">
-        <v>75.80218738162662</v>
+        <v>75.32880314116302</v>
       </c>
       <c r="AM5">
-        <v>145.4371034240303</v>
+        <v>126.5915609224809</v>
       </c>
       <c r="AN5">
-        <v>10.89926278930192</v>
+        <v>11.0759543477595</v>
       </c>
       <c r="AO5">
-        <v>51.9725824740749</v>
+        <v>38.21708791991421</v>
       </c>
       <c r="AP5">
-        <v>944.7620643758955</v>
+        <v>1017.262960292748</v>
       </c>
       <c r="AQ5">
-        <v>224.7444414232783</v>
+        <v>243.7121975814905</v>
       </c>
       <c r="AR5">
-        <v>97.02319763051256</v>
+        <v>103.078293648659</v>
       </c>
       <c r="AS5">
-        <v>4.613012856495013</v>
+        <v>4.884215199540921</v>
       </c>
       <c r="AT5">
-        <v>43.47705911133961</v>
+        <v>51.3558553945801</v>
       </c>
       <c r="AU5">
-        <v>69.58863404246642</v>
+        <v>59.10334709629747</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1159,133 +1159,133 @@
         </is>
       </c>
       <c r="B6">
-        <v>537.4842461897815</v>
+        <v>655.1245160211754</v>
       </c>
       <c r="C6">
-        <v>145.8350233121616</v>
+        <v>152.6399544597918</v>
       </c>
       <c r="D6">
-        <v>6777.820980552787</v>
+        <v>7486.468882972813</v>
       </c>
       <c r="E6">
-        <v>341.9319310618565</v>
+        <v>392.2252068917009</v>
       </c>
       <c r="F6">
-        <v>493.7402550855253</v>
+        <v>602.738713146466</v>
       </c>
       <c r="G6">
-        <v>42.97869166236818</v>
+        <v>50.57100462422067</v>
       </c>
       <c r="H6">
-        <v>16.44112935365808</v>
+        <v>20.86219436456287</v>
       </c>
       <c r="I6">
-        <v>251.1050212750399</v>
+        <v>262.6907070955322</v>
       </c>
       <c r="J6">
-        <v>60.69180419765182</v>
+        <v>64.67121771853994</v>
       </c>
       <c r="K6">
-        <v>4.920998016608243</v>
+        <v>1.601732495660595</v>
       </c>
       <c r="L6">
-        <v>3895.671970125964</v>
+        <v>4350.784243869847</v>
       </c>
       <c r="M6">
-        <v>1865.314142148929</v>
+        <v>2037.038012449112</v>
       </c>
       <c r="N6">
-        <v>1020.207691702378</v>
+        <v>1099.59619158614</v>
       </c>
       <c r="O6">
-        <v>214.8899935457529</v>
+        <v>288.2042390234166</v>
       </c>
       <c r="P6">
-        <v>100.0858426013677</v>
+        <v>77.45819324381939</v>
       </c>
       <c r="Q6">
-        <v>12.644889366042</v>
+        <v>10.83669448517346</v>
       </c>
       <c r="R6">
-        <v>10.3748421753258</v>
+        <v>7.944344908621733</v>
       </c>
       <c r="S6">
-        <v>71.62453265078564</v>
+        <v>63.66864100565061</v>
       </c>
       <c r="T6">
-        <v>39.26290613606073</v>
+        <v>80.77463686077377</v>
       </c>
       <c r="U6">
-        <v>81.74264909013803</v>
+        <v>91.07927843168318</v>
       </c>
       <c r="V6">
-        <v>210.111799864798</v>
+        <v>236.9292741116622</v>
       </c>
       <c r="W6">
-        <v>161.9513043463944</v>
+        <v>195.1443871523528</v>
       </c>
       <c r="Z6">
-        <v>5.873110445206992</v>
+        <v>4.779190905674689</v>
       </c>
       <c r="AA6">
-        <v>18.72954605488631</v>
+        <v>22.46532191115046</v>
       </c>
       <c r="AB6">
-        <v>29.97873730972622</v>
+        <v>34.55861016476546</v>
       </c>
       <c r="AC6">
-        <v>5.230470492887485E-16</v>
+        <v>6.924594925821906E-16</v>
       </c>
       <c r="AD6">
-        <v>9.831693269939914</v>
+        <v>14.5652959687163</v>
       </c>
       <c r="AE6">
-        <v>20.32500479784555</v>
+        <v>22.63233414213729</v>
       </c>
       <c r="AF6">
-        <v>34.21605387891181</v>
+        <v>40.83214436530069</v>
       </c>
       <c r="AG6">
-        <v>4.367556505223785</v>
+        <v>7.321412876908883</v>
       </c>
       <c r="AH6">
-        <v>2566.838227197294</v>
+        <v>2842.818887011155</v>
       </c>
       <c r="AJ6">
-        <v>180.5926039493764</v>
+        <v>189.8783947685966</v>
       </c>
       <c r="AK6">
-        <v>582.8359420469742</v>
+        <v>673.0619068701532</v>
       </c>
       <c r="AL6">
-        <v>123.4677028034574</v>
+        <v>122.1801314291456</v>
       </c>
       <c r="AM6">
-        <v>412.3096269234639</v>
+        <v>370.3258005429651</v>
       </c>
       <c r="AN6">
-        <v>46.24339732547907</v>
+        <v>45.63190787775156</v>
       </c>
       <c r="AO6">
-        <v>167.9305036629727</v>
+        <v>153.1011044779448</v>
       </c>
       <c r="AP6">
-        <v>1459.627252379614</v>
+        <v>1576.905274365517</v>
       </c>
       <c r="AQ6">
-        <v>140.5050215061677</v>
+        <v>150.8406482029782</v>
       </c>
       <c r="AR6">
-        <v>107.2173507749408</v>
+        <v>125.8989403422463</v>
       </c>
       <c r="AS6">
-        <v>13.88469349236327</v>
+        <v>20.98241041130479</v>
       </c>
       <c r="AT6">
-        <v>27.83126489252297</v>
+        <v>32.18726626150264</v>
       </c>
       <c r="AU6">
-        <v>168.6361543834746</v>
+        <v>181.1024672429118</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1298,133 +1298,133 @@
         </is>
       </c>
       <c r="B7">
-        <v>988.4345735663071</v>
+        <v>1085.752846572399</v>
       </c>
       <c r="C7">
-        <v>208.4410696204638</v>
+        <v>212.4242494778784</v>
       </c>
       <c r="D7">
-        <v>4472.339923788291</v>
+        <v>4912.714989390211</v>
       </c>
       <c r="E7">
-        <v>400.1058496559148</v>
+        <v>494.5758167975221</v>
       </c>
       <c r="F7">
-        <v>895.1372764396348</v>
+        <v>984.3839958675363</v>
       </c>
       <c r="G7">
-        <v>89.51591455839484</v>
+        <v>98.99335618180442</v>
       </c>
       <c r="H7">
-        <v>11.8389080408686</v>
+        <v>8.395013833534142</v>
       </c>
       <c r="I7">
-        <v>195.3338376461304</v>
+        <v>197.5152683136388</v>
       </c>
       <c r="J7">
-        <v>84.67186033789245</v>
+        <v>89.60959048298015</v>
       </c>
       <c r="K7">
-        <v>1.943792697940963</v>
+        <v>0.4375086713004407</v>
       </c>
       <c r="L7">
-        <v>2302.348198778277</v>
+        <v>2587.584761962973</v>
       </c>
       <c r="M7">
-        <v>1311.70757181555</v>
+        <v>1398.427650080327</v>
       </c>
       <c r="N7">
-        <v>858.2841531944646</v>
+        <v>926.7025773469107</v>
       </c>
       <c r="O7">
-        <v>211.499464699032</v>
+        <v>279.7863807178488</v>
       </c>
       <c r="P7">
-        <v>130.1550680520241</v>
+        <v>150.8069691030762</v>
       </c>
       <c r="Q7">
-        <v>1.294916635607943</v>
+        <v>1.097495452219324</v>
       </c>
       <c r="R7">
-        <v>6.732185858643055</v>
+        <v>6.797042889225421</v>
       </c>
       <c r="S7">
-        <v>91.30567916064348</v>
+        <v>107.2922988575247</v>
       </c>
       <c r="T7">
-        <v>227.6537197130381</v>
+        <v>249.7668352134913</v>
       </c>
       <c r="U7">
-        <v>86.85443101945022</v>
+        <v>95.74455341344883</v>
       </c>
       <c r="V7">
-        <v>368.9444156277389</v>
+        <v>398.92261732116</v>
       </c>
       <c r="W7">
-        <v>210.6792867080765</v>
+        <v>238.9203875879952</v>
       </c>
       <c r="Z7">
-        <v>1.63579637226008</v>
+        <v>1.356840281743994</v>
       </c>
       <c r="AA7">
-        <v>38.18419059447636</v>
+        <v>41.88727034698501</v>
       </c>
       <c r="AB7">
-        <v>55.72771949001627</v>
+        <v>62.31646679069792</v>
       </c>
       <c r="AC7">
-        <v>-4.254808119462358E-16</v>
+        <v>3.494929764508074E-15</v>
       </c>
       <c r="AD7">
-        <v>3.568046348554198</v>
+        <v>3.315701407346188</v>
       </c>
       <c r="AE7">
-        <v>3.708025370132133</v>
+        <v>0.2333747907199235</v>
       </c>
       <c r="AF7">
-        <v>42.31731530782194</v>
+        <v>28.55198474731266</v>
       </c>
       <c r="AG7">
-        <v>3.464099248606883</v>
+        <v>2.987961533979543</v>
       </c>
       <c r="AH7">
-        <v>1047.023859121402</v>
+        <v>1169.914082112326</v>
       </c>
       <c r="AJ7">
-        <v>230.2721473407974</v>
+        <v>232.7967954340548</v>
       </c>
       <c r="AK7">
-        <v>550.1459947123114</v>
+        <v>595.5795157860723</v>
       </c>
       <c r="AL7">
-        <v>103.929702265379</v>
+        <v>105.8449999624003</v>
       </c>
       <c r="AM7">
-        <v>383.7210684797568</v>
+        <v>416.4263569595025</v>
       </c>
       <c r="AN7">
-        <v>17.65288347883548</v>
+        <v>18.34448102319643</v>
       </c>
       <c r="AO7">
-        <v>63.96840121698035</v>
+        <v>78.48771364439908</v>
       </c>
       <c r="AP7">
-        <v>960.3325067700057</v>
+        <v>1016.304594019886</v>
       </c>
       <c r="AQ7">
-        <v>173.3132575686648</v>
+        <v>187.8029363153236</v>
       </c>
       <c r="AR7">
-        <v>100.5183828926294</v>
+        <v>115.7115487699696</v>
       </c>
       <c r="AS7">
-        <v>5.26441725896477</v>
+        <v>6.961459686174125</v>
       </c>
       <c r="AT7">
-        <v>25.31923278172735</v>
+        <v>22.41076317041736</v>
       </c>
       <c r="AU7">
-        <v>87.14958734064868</v>
+        <v>88.48324198431099</v>
       </c>
       <c r="AV7">
         <v>1</v>
@@ -1437,142 +1437,142 @@
         </is>
       </c>
       <c r="B8">
-        <v>2018.180290670915</v>
+        <v>2173.472033765575</v>
       </c>
       <c r="C8">
-        <v>282.4335843118995</v>
+        <v>306.2583824012307</v>
       </c>
       <c r="D8">
-        <v>2977.957772341208</v>
+        <v>3149.658127513449</v>
       </c>
       <c r="E8">
-        <v>498.7227031586557</v>
+        <v>562.4465747037281</v>
       </c>
       <c r="F8">
-        <v>1883.160899698387</v>
+        <v>2031.370184699351</v>
       </c>
       <c r="G8">
-        <v>134.9449487214098</v>
+        <v>142.0501451674864</v>
       </c>
       <c r="H8">
-        <v>0.3573228053679208</v>
+        <v>0.248178713941402</v>
       </c>
       <c r="I8">
-        <v>186.767282884677</v>
+        <v>205.8604689406994</v>
       </c>
       <c r="J8">
-        <v>97.3009660569183</v>
+        <v>102.1286082956877</v>
       </c>
       <c r="K8">
-        <v>0.6727522796971759</v>
+        <v>0.6351752069392425</v>
       </c>
       <c r="L8">
-        <v>1267.348215442721</v>
+        <v>1331.359005791895</v>
       </c>
       <c r="M8">
-        <v>1142.987317072495</v>
+        <v>1206.076249075914</v>
       </c>
       <c r="N8">
-        <v>567.622239825992</v>
+        <v>612.2228726456411</v>
       </c>
       <c r="O8">
-        <v>255.113284197509</v>
+        <v>300.5836752163556</v>
       </c>
       <c r="P8">
-        <v>93.81298748228598</v>
+        <v>102.3025006975543</v>
       </c>
       <c r="Q8">
-        <v>0.008373221335627283</v>
+        <v>0.0224803645113867</v>
       </c>
       <c r="R8">
-        <v>0.5472363253479948</v>
+        <v>0.6034492826359908</v>
       </c>
       <c r="S8">
-        <v>155.6248431577247</v>
+        <v>170.1773203352726</v>
       </c>
       <c r="T8">
-        <v>504.2612314259195</v>
+        <v>524.6136166784396</v>
       </c>
       <c r="U8">
-        <v>140.357187644996</v>
+        <v>148.8958379893172</v>
       </c>
       <c r="V8">
-        <v>844.6014170507544</v>
+        <v>935.5806193128307</v>
       </c>
       <c r="W8">
-        <v>296.5408943638947</v>
+        <v>316.857306735617</v>
       </c>
       <c r="X8">
-        <v>3928.699041553994</v>
+        <v>4203.961932344067</v>
       </c>
       <c r="Y8">
-        <v>619.6702869300105</v>
+        <v>660.8749918098674</v>
       </c>
       <c r="Z8">
-        <v>6.361809080392298</v>
+        <v>4.767260171636059</v>
       </c>
       <c r="AA8">
-        <v>45.87169657607331</v>
+        <v>47.45533010544715</v>
       </c>
       <c r="AB8">
-        <v>95.01146895502555</v>
+        <v>98.70763310821485</v>
       </c>
       <c r="AC8">
-        <v>4.736813870670964E-15</v>
+        <v>-3.659409320620845E-15</v>
       </c>
       <c r="AD8">
-        <v>0.3840391087436775</v>
+        <v>0.2687985633066516</v>
       </c>
       <c r="AE8">
-        <v>0.04635095690185447</v>
+        <v>0.04901506045664716</v>
       </c>
       <c r="AF8">
-        <v>0.0009456479956068093</v>
+        <v>0.006598418072300684</v>
       </c>
       <c r="AG8">
-        <v>0.4072322654398939</v>
+        <v>0.2711274270150539</v>
       </c>
       <c r="AH8">
-        <v>406.4761638928753</v>
+        <v>452.9770658247603</v>
       </c>
       <c r="AI8">
-        <v>429.4473048975834</v>
+        <v>467.5037520550409</v>
       </c>
       <c r="AJ8">
-        <v>152.2785787699081</v>
+        <v>150.1431400328628</v>
       </c>
       <c r="AK8">
-        <v>534.8371049198915</v>
+        <v>571.1011063097244</v>
       </c>
       <c r="AL8">
-        <v>57.12232289078364</v>
+        <v>58.37067639681481</v>
       </c>
       <c r="AM8">
-        <v>67.65031878470283</v>
+        <v>52.79372514756093</v>
       </c>
       <c r="AN8">
-        <v>10.65111365125977</v>
+        <v>11.1987212918016</v>
       </c>
       <c r="AO8">
-        <v>48.41516923547776</v>
+        <v>31.29087345525915</v>
       </c>
       <c r="AP8">
-        <v>749.0310421635769</v>
+        <v>801.0911844051889</v>
       </c>
       <c r="AQ8">
-        <v>245.1654713906665</v>
+        <v>262.2888789653043</v>
       </c>
       <c r="AR8">
-        <v>97.92326159680476</v>
+        <v>105.8028510103679</v>
       </c>
       <c r="AS8">
-        <v>3.818370056836754</v>
+        <v>4.374063280867016</v>
       </c>
       <c r="AT8">
-        <v>27.28837246098082</v>
+        <v>26.62945428328844</v>
       </c>
       <c r="AU8">
-        <v>65.84553806338359</v>
+        <v>54.19507953326998</v>
       </c>
       <c r="AV8">
         <v>1</v>
@@ -1585,133 +1585,133 @@
         </is>
       </c>
       <c r="B9">
-        <v>569.6609143601266</v>
+        <v>767.9346267595233</v>
       </c>
       <c r="C9">
-        <v>196.3954141178781</v>
+        <v>210.5585392067447</v>
       </c>
       <c r="D9">
-        <v>10886.22149975636</v>
+        <v>11983.96398825761</v>
       </c>
       <c r="E9">
-        <v>544.6019384373367</v>
+        <v>651.6599878211069</v>
       </c>
       <c r="F9">
-        <v>524.5863053096084</v>
+        <v>715.7050314163776</v>
       </c>
       <c r="G9">
-        <v>43.4222564597075</v>
+        <v>50.46506258527391</v>
       </c>
       <c r="H9">
-        <v>25.11360082937176</v>
+        <v>22.80098477608593</v>
       </c>
       <c r="I9">
-        <v>389.4884775208669</v>
+        <v>418.1970875207778</v>
       </c>
       <c r="J9">
-        <v>56.70997555983801</v>
+        <v>61.53501628698417</v>
       </c>
       <c r="K9">
-        <v>11.93323607781261</v>
+        <v>3.463110527433995</v>
       </c>
       <c r="L9">
-        <v>7023.8522470486</v>
+        <v>7788.933622213286</v>
       </c>
       <c r="M9">
-        <v>2808.002398538198</v>
+        <v>3073.37517811332</v>
       </c>
       <c r="N9">
-        <v>1060.778139170534</v>
+        <v>1123.4455393882</v>
       </c>
       <c r="O9">
-        <v>350.1000039197069</v>
+        <v>518.7389279114377</v>
       </c>
       <c r="P9">
-        <v>197.198027178817</v>
+        <v>101.5392577399149</v>
       </c>
       <c r="Q9">
-        <v>18.2927043766263</v>
+        <v>25.30651198097452</v>
       </c>
       <c r="R9">
-        <v>9.905981423368763</v>
+        <v>9.027229819320794</v>
       </c>
       <c r="S9">
-        <v>79.24636836529467</v>
+        <v>75.14114614404288</v>
       </c>
       <c r="T9">
-        <v>-32.40733199177335</v>
+        <v>73.31053198154818</v>
       </c>
       <c r="U9">
-        <v>114.5705184795863</v>
+        <v>117.1931130390689</v>
       </c>
       <c r="V9">
-        <v>208.3119337913921</v>
+        <v>242.1412292353831</v>
       </c>
       <c r="W9">
-        <v>236.1452758554489</v>
+        <v>286.0071070104685</v>
       </c>
       <c r="Z9">
-        <v>5.069081308710468</v>
+        <v>5.129131918243649</v>
       </c>
       <c r="AA9">
-        <v>17.9485946501212</v>
+        <v>21.11436135146404</v>
       </c>
       <c r="AB9">
-        <v>31.77069098308254</v>
+        <v>35.87134139909339</v>
       </c>
       <c r="AC9">
-        <v>-1.411205608247241E-16</v>
+        <v>-2.750118031423882E-16</v>
       </c>
       <c r="AD9">
-        <v>23.09070299813175</v>
+        <v>20.0527367317355</v>
       </c>
       <c r="AE9">
-        <v>3.206873142505311</v>
+        <v>5.574881667639606</v>
       </c>
       <c r="AF9">
-        <v>32.26832174013555</v>
+        <v>30.72774779718558</v>
       </c>
       <c r="AG9">
-        <v>17.62341852200554</v>
+        <v>18.3295096855947</v>
       </c>
       <c r="AH9">
-        <v>5643.511389874981</v>
+        <v>6241.568123674253</v>
       </c>
       <c r="AJ9">
-        <v>225.3887048897294</v>
+        <v>217.6429997790304</v>
       </c>
       <c r="AK9">
-        <v>653.0763784664238</v>
+        <v>763.2603227345894</v>
       </c>
       <c r="AL9">
-        <v>130.4702712734644</v>
+        <v>122.8815370689273</v>
       </c>
       <c r="AM9">
-        <v>223.1189644683637</v>
+        <v>194.3323147606544</v>
       </c>
       <c r="AN9">
-        <v>70.30844509647763</v>
+        <v>72.44073640272347</v>
       </c>
       <c r="AO9">
-        <v>271.5522883679185</v>
+        <v>222.6702934260946</v>
       </c>
       <c r="AP9">
-        <v>2246.674318629287</v>
+        <v>2415.767453792488</v>
       </c>
       <c r="AQ9">
-        <v>155.8869739301279</v>
+        <v>164.7843804602247</v>
       </c>
       <c r="AR9">
-        <v>155.7886049617408</v>
+        <v>187.7415628715854</v>
       </c>
       <c r="AS9">
-        <v>23.75300678785245</v>
+        <v>39.23078375919189</v>
       </c>
       <c r="AT9">
-        <v>55.2371535078866</v>
+        <v>52.83126191278017</v>
       </c>
       <c r="AU9">
-        <v>281.4650485865852</v>
+        <v>293.7505985056381</v>
       </c>
       <c r="AV9">
         <v>1</v>
